--- a/analysis/aggregate/ac-PRF.xlsx
+++ b/analysis/aggregate/ac-PRF.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -518,22 +518,22 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7979117605724549</v>
+        <v>0.7628361810666193</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02630474341726022</v>
+        <v>0.01158194176832889</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7929411764705883</v>
+        <v>0.7564705882352941</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02054617552538</v>
+        <v>0.008921029934178263</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7953442886268538</v>
+        <v>0.7596117747476989</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02196473464022954</v>
+        <v>0.008927422050968992</v>
       </c>
     </row>
     <row r="3">
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -571,22 +571,22 @@
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7979117605724549</v>
+        <v>0.7019070427318238</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02630474341726022</v>
+        <v>0.0129895994446469</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7929411764705883</v>
+        <v>0.7035294117647058</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02054617552538</v>
+        <v>0.0121979066784281</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7953442886268538</v>
+        <v>0.7027086223504331</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02196473464022954</v>
+        <v>0.01230075357459118</v>
       </c>
     </row>
     <row r="4">
@@ -597,7 +597,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -624,22 +624,22 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7946384282584276</v>
+        <v>0.7645535610693981</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02215577199420941</v>
+        <v>0.01748613562702413</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7905882352941177</v>
+        <v>0.76</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01068582477916766</v>
+        <v>0.01464694070351614</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7925445230105735</v>
+        <v>0.762264620148735</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01535006605215245</v>
+        <v>0.01595534167926884</v>
       </c>
     </row>
     <row r="5">
@@ -650,7 +650,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -677,22 +677,22 @@
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7946384282584276</v>
+        <v>0.6978614358393845</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02215577199420941</v>
+        <v>0.02486904288646526</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7905882352941177</v>
+        <v>0.7035294117647058</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01068582477916766</v>
+        <v>0.02338189048747269</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7925445230105735</v>
+        <v>0.7006680369052052</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01535006605215245</v>
+        <v>0.02384425735629462</v>
       </c>
     </row>
     <row r="6">
@@ -703,7 +703,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -727,25 +727,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8186567456362652</v>
+        <v>0.7909247228180893</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007220599924965905</v>
+        <v>0.01388019588585022</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8057142857142857</v>
+        <v>0.7691428571428572</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008081220356417699</v>
+        <v>0.01315527363796723</v>
       </c>
       <c r="L6" t="n">
-        <v>0.812091021285785</v>
+        <v>0.7798398540520636</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003552758547473675</v>
+        <v>0.01190036491214692</v>
       </c>
     </row>
     <row r="7">
@@ -756,7 +756,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -783,22 +783,22 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8162890328726485</v>
+        <v>0.7909247228180893</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008193480097753366</v>
+        <v>0.01388019588585022</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8068571428571427</v>
+        <v>0.7691428571428572</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007450517034517296</v>
+        <v>0.01315527363796723</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8114961788519899</v>
+        <v>0.7798398540520636</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003351978158894027</v>
+        <v>0.01190036491214692</v>
       </c>
     </row>
     <row r="8">
@@ -809,7 +809,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -836,22 +836,22 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8157392026578073</v>
+        <v>0.7499324435148262</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01143414204462839</v>
+        <v>0.02668125337544833</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7942857142857143</v>
+        <v>0.7588571428571429</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0193780856660722</v>
+        <v>0.01779704171702564</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8047992775629075</v>
+        <v>0.7542292479962034</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01364890851437444</v>
+        <v>0.01966583541848766</v>
       </c>
     </row>
     <row r="9">
@@ -862,48 +862,472 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>flan-t5-base</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7499324435148262</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02668125337544833</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7588571428571429</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01779704171702564</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7542292479962034</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.01966583541848766</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>t5-base</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7979117605724549</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.02630474341726022</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7929411764705883</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.02054617552538</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7953442886268538</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.02196473464022954</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7979117605724549</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.02630474341726022</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7929411764705883</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.02054617552538</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.7953442886268538</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.02196473464022954</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7946384282584276</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.02215577199420941</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7905882352941177</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.01068582477916766</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7925445230105735</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.01535006605215245</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7946384282584276</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.02215577199420941</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7905882352941177</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.01068582477916766</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.7925445230105735</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.01535006605215245</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>paraphrase</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8186567456362652</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.007220599924965905</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8057142857142857</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.008081220356417699</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.812091021285785</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.003552758547473675</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8162890328726485</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.008193480097753366</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.8068571428571427</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.007450517034517296</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.8114961788519899</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.003351978158894027</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.8157392026578073</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I16" t="n">
         <v>0.01143414204462839</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J16" t="n">
         <v>0.7942857142857143</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K16" t="n">
         <v>0.0193780856660722</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L16" t="n">
         <v>0.8047992775629075</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M16" t="n">
+        <v>0.01364890851437444</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8157392026578073</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.01143414204462839</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0193780856660722</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.8047992775629075</v>
+      </c>
+      <c r="M17" t="n">
         <v>0.01364890851437444</v>
       </c>
     </row>

--- a/analysis/aggregate/ac-PRF.xlsx
+++ b/analysis/aggregate/ac-PRF.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -518,22 +518,22 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7628361810666193</v>
+        <v>0.7759889143647976</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01158194176832889</v>
+        <v>0.03186679009088352</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7564705882352941</v>
+        <v>0.768235294117647</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008921029934178263</v>
+        <v>0.02145245003389467</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7596117747476989</v>
+        <v>0.7720094910551094</v>
       </c>
       <c r="M2" t="n">
-        <v>0.008927422050968992</v>
+        <v>0.02560257284789822</v>
       </c>
     </row>
     <row r="3">
@@ -554,39 +554,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7019070427318238</v>
+        <v>0.7702886756048087</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0129895994446469</v>
+        <v>0.01216676155822163</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7035294117647058</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0121979066784281</v>
+        <v>0.01176470588235294</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7027086223504331</v>
+        <v>0.7674157623767675</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01230075357459118</v>
+        <v>0.008565928406441768</v>
       </c>
     </row>
     <row r="4">
@@ -612,7 +612,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -624,22 +624,22 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7645535610693981</v>
+        <v>0.7699335642954763</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01748613562702413</v>
+        <v>0.02499191533635829</v>
       </c>
       <c r="J4" t="n">
-        <v>0.76</v>
+        <v>0.7623529411764707</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01464694070351614</v>
+        <v>0.01642851769855169</v>
       </c>
       <c r="L4" t="n">
-        <v>0.762264620148735</v>
+        <v>0.7660446755512715</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01595534167926884</v>
+        <v>0.01916198333272108</v>
       </c>
     </row>
     <row r="5">
@@ -670,29 +670,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6978614358393845</v>
+        <v>0.7633106638694743</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02486904288646526</v>
+        <v>0.01499691063642221</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7035294117647058</v>
+        <v>0.7623529411764706</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02338189048747269</v>
+        <v>0.01354219345084862</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7006680369052052</v>
+        <v>0.7628121577403618</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02384425735629462</v>
+        <v>0.01362949287380281</v>
       </c>
     </row>
     <row r="6">
@@ -730,22 +730,22 @@
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7909247228180893</v>
+        <v>0.7819833100010335</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01388019588585022</v>
+        <v>0.01260262927311689</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7691428571428572</v>
+        <v>0.7668571428571429</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01315527363796723</v>
+        <v>0.0233517905619458</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7798398540520636</v>
+        <v>0.7742762991174907</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01190036491214692</v>
+        <v>0.01710147790392485</v>
       </c>
     </row>
     <row r="7">
@@ -771,34 +771,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7909247228180893</v>
+        <v>0.7731589839588976</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01388019588585022</v>
+        <v>0.01314853035365245</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7691428571428572</v>
+        <v>0.752</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01315527363796723</v>
+        <v>0.01695131082764724</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7798398540520636</v>
+        <v>0.7624237094398205</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01190036491214692</v>
+        <v>0.01495968233120615</v>
       </c>
     </row>
     <row r="8">
@@ -819,12 +819,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -836,22 +836,22 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7499324435148262</v>
+        <v>0.7835981297285872</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02668125337544833</v>
+        <v>0.00657014457145408</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7588571428571429</v>
+        <v>0.7657142857142857</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01779704171702564</v>
+        <v>0.01277753129999883</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7542292479962034</v>
+        <v>0.7745343920531087</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01966583541848766</v>
+        <v>0.009357613120831939</v>
       </c>
     </row>
     <row r="9">
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -882,29 +882,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7499324435148262</v>
+        <v>0.768504717808238</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02668125337544833</v>
+        <v>0.01619103553235011</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7588571428571429</v>
+        <v>0.7542857142857142</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01779704171702564</v>
+        <v>0.01399708424447527</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7542292479962034</v>
+        <v>0.7612597572519914</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01966583541848766</v>
+        <v>0.01269023246414791</v>
       </c>
     </row>
     <row r="10">
@@ -925,7 +925,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -942,22 +942,22 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7979117605724549</v>
+        <v>0.7901920395695406</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02630474341726022</v>
+        <v>0.03429817478840256</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7929411764705883</v>
+        <v>0.7823529411764706</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02054617552538</v>
+        <v>0.01315334104411645</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7953442886268538</v>
+        <v>0.7858193909207959</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02196473464022954</v>
+        <v>0.01504112554333517</v>
       </c>
     </row>
     <row r="11">
@@ -978,39 +978,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7979117605724549</v>
+        <v>0.7796680784439497</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02630474341726022</v>
+        <v>0.01490919711098299</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7929411764705883</v>
+        <v>0.7858823529411765</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02054617552538</v>
+        <v>0.01793876550820817</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7953442886268538</v>
+        <v>0.7826344666569633</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02196473464022954</v>
+        <v>0.01207496426143413</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1048,22 +1048,22 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7946384282584276</v>
+        <v>0.7934458801627304</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02215577199420941</v>
+        <v>0.01532945167698434</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7905882352941177</v>
+        <v>0.7858823529411765</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01068582477916766</v>
+        <v>0.01068582477916762</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7925445230105735</v>
+        <v>0.789627525125751</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01535006605215245</v>
+        <v>0.01246544342141601</v>
       </c>
     </row>
     <row r="13">
@@ -1094,29 +1094,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7946384282584276</v>
+        <v>0.7824890253928366</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02215577199420941</v>
+        <v>0.01433880487162856</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7905882352941177</v>
+        <v>0.7870588235294118</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01068582477916766</v>
+        <v>0.01464694070351622</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7925445230105735</v>
+        <v>0.7847488058659879</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01535006605215245</v>
+        <v>0.01387239862028402</v>
       </c>
     </row>
     <row r="14">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1151,25 +1151,25 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8186567456362652</v>
+        <v>0.8147884327788443</v>
       </c>
       <c r="I14" t="n">
-        <v>0.007220599924965905</v>
+        <v>0.009756971543303797</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8057142857142857</v>
+        <v>0.8045714285714286</v>
       </c>
       <c r="K14" t="n">
-        <v>0.008081220356417699</v>
+        <v>0.0130305762868473</v>
       </c>
       <c r="L14" t="n">
-        <v>0.812091021285785</v>
+        <v>0.8096412598311872</v>
       </c>
       <c r="M14" t="n">
-        <v>0.003552758547473675</v>
+        <v>0.01126940583748925</v>
       </c>
     </row>
     <row r="15">
@@ -1190,39 +1190,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8162890328726485</v>
+        <v>0.8101310710803645</v>
       </c>
       <c r="I15" t="n">
-        <v>0.008193480097753366</v>
+        <v>0.01798885220060057</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8068571428571427</v>
+        <v>0.8045714285714286</v>
       </c>
       <c r="K15" t="n">
-        <v>0.007450517034517296</v>
+        <v>0.01869191683862417</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8114961788519899</v>
+        <v>0.8073326312209611</v>
       </c>
       <c r="M15" t="n">
-        <v>0.003351978158894027</v>
+        <v>0.01810206853188335</v>
       </c>
     </row>
     <row r="16">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1260,22 +1260,22 @@
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8157392026578073</v>
+        <v>0.823261689769366</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01143414204462839</v>
+        <v>0.0175204085628956</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7942857142857143</v>
+        <v>0.7965714285714285</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0193780856660722</v>
+        <v>0.01251937274297525</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8047992775629075</v>
+        <v>0.8095559633321203</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01364890851437444</v>
+        <v>0.009390417384082165</v>
       </c>
     </row>
     <row r="17">
@@ -1306,29 +1306,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8157392026578073</v>
+        <v>0.8267651324193013</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01143414204462839</v>
+        <v>0.01087867294839794</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7942857142857143</v>
+        <v>0.801142857142857</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0193780856660722</v>
+        <v>0.01533303755999859</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8047992775629075</v>
+        <v>0.8136648790207985</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01364890851437444</v>
+        <v>0.009544293407475436</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/aggregate/ac-PRF.xlsx
+++ b/analysis/aggregate/ac-PRF.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,32 +454,92 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>precision_mean</t>
+          <t>micro_precision_mean</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>precision_std</t>
+          <t>micro_precision_std</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>recall_mean</t>
+          <t>micro_recall_mean</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>recall_std</t>
+          <t>micro_recall_std</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>f1_mean</t>
+          <t>micro_f1_mean</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>f1_std</t>
+          <t>micro_f1_std</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>macro_precision_mean</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>macro_precision_std</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>macro_recall_mean</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>macro_recall_std</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>macro_f1_mean</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>macro_f1_std</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>weighted_precision_mean</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>weighted_precision_std</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>weighted_recall_mean</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>weighted_recall_std</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>weighted_f1_mean</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>weighted_f1_std</t>
         </is>
       </c>
     </row>
@@ -518,22 +578,58 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7759889143647976</v>
+        <v>0.7996307613182195</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03186679009088352</v>
+        <v>0.02840002076237245</v>
       </c>
       <c r="J2" t="n">
-        <v>0.768235294117647</v>
+        <v>0.7917647058823529</v>
       </c>
       <c r="K2" t="n">
         <v>0.02145245003389467</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7720094910551094</v>
+        <v>0.7955929373036216</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02560257284789822</v>
+        <v>0.0234327034776529</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.8074380165289258</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.02577635178419081</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.7991735537190083</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.02348474750145916</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.7969146005509642</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.02410932658936074</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.8176470588235295</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.02660640538257241</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.7917647058823529</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.02145245003389467</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.7962745098039214</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.02285470547777787</v>
       </c>
     </row>
     <row r="3">
@@ -571,22 +667,58 @@
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7702886756048087</v>
+        <v>0.7986829786582421</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01216676155822163</v>
+        <v>0.01298648499302245</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.7929411764705883</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01176470588235294</v>
+        <v>0.01578400925293967</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7674157623767675</v>
+        <v>0.7957288602358014</v>
       </c>
       <c r="M3" t="n">
-        <v>0.008565928406441768</v>
+        <v>0.01178149921658891</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8041322314049587</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.01416122662531668</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.7994490358126722</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.02014036002912863</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.7950964187327824</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.0167879158563178</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.815686274509804</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.01218608126927066</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.7929411764705883</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.01578400925293967</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.7959999999999999</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.01328248666981431</v>
       </c>
     </row>
     <row r="4">
@@ -624,22 +756,58 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7699335642954763</v>
+        <v>0.7946832334670746</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02499191533635829</v>
+        <v>0.01415100929603985</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7623529411764707</v>
+        <v>0.7870588235294117</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01642851769855169</v>
+        <v>0.01522609306534682</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7660446755512715</v>
+        <v>0.7907701414629008</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01916198333272108</v>
+        <v>0.01154711643016212</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.8055096418732784</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.01198426266344696</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.7986225895316805</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.01516403189479105</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.7954269972451791</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.01274026503446117</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.8109803921568629</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.01288386000078388</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.7870588235294117</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.01522609306534682</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.790392156862745</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.01271338437446851</v>
       </c>
     </row>
     <row r="5">
@@ -677,22 +845,58 @@
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7633106638694743</v>
+        <v>0.795044674503519</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01499691063642221</v>
+        <v>0.002432979008209552</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7623529411764706</v>
+        <v>0.7941176470588236</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01354219345084862</v>
+        <v>0.01018853416216988</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7628121577403618</v>
+        <v>0.7945605444655439</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01362949287380281</v>
+        <v>0.005853441634360803</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.8027548209366392</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01162260226431346</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.800550964187328</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.01565649833430613</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.7948209366391185</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.01307219864804492</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.8125490196078433</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.005606266060978734</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.7941176470588236</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.01018853416216988</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.7950588235294117</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.007597122019276659</v>
       </c>
     </row>
     <row r="6">
@@ -730,22 +934,58 @@
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7819833100010335</v>
+        <v>0.7949152603466059</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01260262927311689</v>
+        <v>0.006973113726028617</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7668571428571429</v>
+        <v>0.7794285714285715</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0233517905619458</v>
+        <v>0.01543914981269289</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7742762991174907</v>
+        <v>0.7870243082412156</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01710147790392485</v>
+        <v>0.008829186575560304</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.803305785123967</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.007616345069393522</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.788154269972452</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.01275128023254337</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.7887367178276269</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.009606646811709134</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.8144761904761906</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.005023753102820173</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.7794285714285715</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.01543914981269289</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.7875319727891157</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00904763746098064</v>
       </c>
     </row>
     <row r="7">
@@ -783,22 +1023,58 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7731589839588976</v>
+        <v>0.7907996499341614</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01314853035365245</v>
+        <v>0.008852535253807159</v>
       </c>
       <c r="J7" t="n">
-        <v>0.752</v>
+        <v>0.7691428571428571</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01695131082764724</v>
+        <v>0.01315527363796724</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7624237094398205</v>
+        <v>0.7798117795862768</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01495968233120615</v>
+        <v>0.01089973664575185</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.8023415977961432</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.008177921547546771</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.7812672176308542</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.01289921186605301</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.7846753246753246</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.01083347446529644</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.8153333333333332</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.004074142787849053</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.7691428571428571</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.01315527363796724</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.7819646258503401</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.009596928257386133</v>
       </c>
     </row>
     <row r="8">
@@ -836,22 +1112,58 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7835981297285872</v>
+        <v>0.7999808916474993</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00657014457145408</v>
+        <v>0.007887793354111716</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7657142857142857</v>
+        <v>0.7817142857142857</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01277753129999883</v>
+        <v>0.01303057628684734</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7745343920531087</v>
+        <v>0.7907231018785239</v>
       </c>
       <c r="M8" t="n">
-        <v>0.009357613120831939</v>
+        <v>0.009965390468354859</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.8087878787878788</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.01213271117468634</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.7920110192837467</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01328326551100957</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.7932310114128296</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.01378337799944693</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.8205142857142856</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.00869399146125318</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.7817142857142857</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.01303057628684734</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.7912163265306121</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.0120850549789112</v>
       </c>
     </row>
     <row r="9">
@@ -889,22 +1201,58 @@
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.768504717808238</v>
+        <v>0.7882588932728263</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01619103553235011</v>
+        <v>0.01618044621554864</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7542857142857142</v>
+        <v>0.7737142857142858</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01399708424447527</v>
+        <v>0.01646269747530052</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7612597572519914</v>
+        <v>0.7808480342797652</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01269023246414791</v>
+        <v>0.01400149426216317</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.7935261707988982</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01602923519982016</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.7793388429752068</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.01685288586135846</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.777914207005116</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.01648086658417077</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.814952380952381</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.0118312013026166</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.7737142857142858</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.01646269747530052</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.7831782312925171</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.01408912219902059</v>
       </c>
     </row>
     <row r="10">
@@ -942,22 +1290,58 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7901920395695406</v>
+        <v>0.8181738580456723</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03429817478840256</v>
+        <v>0.02213493717804725</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7823529411764706</v>
+        <v>0.8105882352941176</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01315334104411645</v>
+        <v>0.02255328177962446</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7858193909207959</v>
+        <v>0.8139220161129973</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01504112554333517</v>
+        <v>0.007621271306186866</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.8292011019283748</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.006817833978382564</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.824793388429752</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.01748823167835148</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.8203305785123967</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.007780601471642407</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.831764705882353</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.008730445827801178</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.8105882352941176</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.02255328177962446</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.8127450980392157</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.01253522526150951</v>
       </c>
     </row>
     <row r="11">
@@ -995,22 +1379,58 @@
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7796680784439497</v>
+        <v>0.7960197727498228</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01490919711098299</v>
+        <v>0.0131867732128598</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7858823529411765</v>
+        <v>0.8023529411764706</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01793876550820817</v>
+        <v>0.01589324245424271</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7826344666569633</v>
+        <v>0.7990424464362812</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01207496426143413</v>
+        <v>0.008987999930993393</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.8068870523415977</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.006982805430102842</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.8112947658402204</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.01763946070918135</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.8022117276662731</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.0109241905185571</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.8123529411764707</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.01205922205622348</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.8023529411764706</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.01589324245424271</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.7994677871148459</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.01040400390806008</v>
       </c>
     </row>
     <row r="12">
@@ -1048,22 +1468,58 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7934458801627304</v>
+        <v>0.8124243163809302</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01532945167698434</v>
+        <v>0.01222130462073859</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7858823529411765</v>
+        <v>0.8047058823529412</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01068582477916762</v>
+        <v>0.008724939396583132</v>
       </c>
       <c r="L12" t="n">
-        <v>0.789627525125751</v>
+        <v>0.8085278369113986</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01246544342141601</v>
+        <v>0.009659894518436421</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.8217630853994493</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.01485433577360094</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.8134986225895318</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.01355192713636235</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.8120110192837464</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.01355976482776429</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.8262745098039218</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.009640799818776113</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.8047058823529412</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.008724939396583132</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.8076470588235292</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.007042464704340294</v>
       </c>
     </row>
     <row r="13">
@@ -1101,22 +1557,58 @@
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7824890253928366</v>
+        <v>0.8058767378055223</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01433880487162856</v>
+        <v>0.01453161396268812</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7870588235294118</v>
+        <v>0.8105882352941176</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01464694070351622</v>
+        <v>0.01522609306534682</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7847488058659879</v>
+        <v>0.8082064698892057</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01387239862028402</v>
+        <v>0.01422079756081557</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.8121212121212122</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.01453151723956247</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.8162534435261708</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.01727538522877485</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.8074380165289256</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.01505730792636044</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.8190196078431373</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.01179734035803248</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.8105882352941176</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.01522609306534682</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.8067450980392156</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.01262050716399731</v>
       </c>
     </row>
     <row r="14">
@@ -1154,22 +1646,58 @@
         <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8147884327788443</v>
+        <v>0.8217317261661229</v>
       </c>
       <c r="I14" t="n">
-        <v>0.009756971543303797</v>
+        <v>0.01090307796378055</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8045714285714286</v>
+        <v>0.8114285714285714</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0130305762868473</v>
+        <v>0.0139970842444753</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8096412598311872</v>
+        <v>0.8165411621499319</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01126940583748925</v>
+        <v>0.01232279771231268</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.8327823691460056</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.007782673876868674</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.8209366391184574</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.008546607194208534</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.8201338055883511</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.009375340903602604</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.8411428571428571</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.008238232864250936</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.0139970842444753</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.8174965986394558</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.01293418947746742</v>
       </c>
     </row>
     <row r="15">
@@ -1207,22 +1735,58 @@
         <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8101310710803645</v>
+        <v>0.82165235982819</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01798885220060057</v>
+        <v>0.01304868337254576</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8045714285714286</v>
+        <v>0.8160000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01869191683862417</v>
+        <v>0.0130305762868473</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8073326312209611</v>
+        <v>0.8188072366088459</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01810206853188335</v>
+        <v>0.01267994628020879</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.8318181818181818</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.01797507467521741</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.8209366391184574</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.01809080652419236</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.8201416765053129</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.01769272889161548</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.8414285714285714</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.01217782081194702</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.8160000000000001</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.0130305762868473</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.8209414965986394</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.0118665290827459</v>
       </c>
     </row>
     <row r="16">
@@ -1260,22 +1824,58 @@
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.823261689769366</v>
+        <v>0.8327769521145786</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0175204085628956</v>
+        <v>0.01866103029668079</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7965714285714285</v>
+        <v>0.8057142857142857</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01251937274297525</v>
+        <v>0.008081220356417661</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8095559633321203</v>
+        <v>0.8188799441353914</v>
       </c>
       <c r="M16" t="n">
-        <v>0.009390417384082165</v>
+        <v>0.007557715298321053</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.8398071625344354</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0164541467317003</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.8223140495867769</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.008979617638020167</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.8243368752459661</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.01058706358480803</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.844095238095238</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.01676704466649011</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.8057142857142857</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.008081220356417661</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.8156625850340135</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.006136690918313028</v>
       </c>
     </row>
     <row r="17">
@@ -1313,22 +1913,58 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8267651324193013</v>
+        <v>0.8410016922996488</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01087867294839794</v>
+        <v>0.01247978376807773</v>
       </c>
       <c r="J17" t="n">
-        <v>0.801142857142857</v>
+        <v>0.8148571428571429</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01533303755999859</v>
+        <v>0.01038051549976287</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8136648790207985</v>
+        <v>0.8276336259025058</v>
       </c>
       <c r="M17" t="n">
-        <v>0.009544293407475436</v>
+        <v>0.006117413334624744</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.8425619834710745</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.01066492910966904</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.8253443526170801</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.010371818510753</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.8278630460448643</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.01010401661643823</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.8520952380952382</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.00866090860524924</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.8148571428571429</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.01038051549976287</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.825643537414966</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.007737791875641357</v>
       </c>
     </row>
   </sheetData>
